--- a/VT_Model_DMD_V01.xlsx
+++ b/VT_Model_DMD_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasiu\Desktop\Praca Magisterska\Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasiu\Desktop\PracaMag\Polska\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3DC65A-5ED2-4389-BA3C-AC4A087FCAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955194D8-FD7F-4B96-8D57-F8B05A9F0F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEC_Comm" sheetId="112" r:id="rId1"/>
@@ -809,7 +809,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="83">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1055,6 +1055,9 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>Annual Demand Value [PJ]</t>
   </si>
 </sst>
 </file>
@@ -5288,7 +5291,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6265,7 +6268,7 @@
     <xdr:to>
       <xdr:col>52</xdr:col>
       <xdr:colOff>373574</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>105640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6781,22 +6784,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:J22"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" customWidth="1"/>
+    <col min="11" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="18">
+    <row r="2" spans="2:10" ht="17.399999999999999">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -6818,7 +6821,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="2:10" ht="17.649999999999999" customHeight="1">
+    <row r="4" spans="2:10" ht="17.7" customHeight="1">
       <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
@@ -6977,7 +6980,7 @@
     <row r="13" spans="2:10">
       <c r="B13" s="1"/>
     </row>
-    <row r="22" ht="13.9" customHeight="1"/>
+    <row r="22" ht="13.95" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6990,15 +6993,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:J8"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" customWidth="1"/>
     <col min="6" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7068,7 +7071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="38.25">
+    <row r="6" spans="2:10" ht="39.6">
       <c r="B6" s="32" t="s">
         <v>41</v>
       </c>
@@ -7155,25 +7158,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AC42"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="C1" s="23"/>
     </row>
-    <row r="3" spans="2:13" ht="18">
+    <row r="3" spans="2:13" ht="17.399999999999999">
       <c r="B3" s="16" t="s">
         <v>56</v>
       </c>
@@ -7409,6 +7412,80 @@
         <v>167484</v>
       </c>
     </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="21">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="21">
+        <v>2025</v>
+      </c>
+      <c r="E22" s="21">
+        <v>2030</v>
+      </c>
+      <c r="F22" s="21">
+        <v>2035</v>
+      </c>
+      <c r="G22" s="21">
+        <v>2040</v>
+      </c>
+      <c r="H22" s="21">
+        <v>2045</v>
+      </c>
+      <c r="I22" s="21">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="26.4">
+      <c r="B23" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <f>C8*0.0036</f>
+        <v>395.99891185173067</v>
+      </c>
+      <c r="D24">
+        <f t="shared" ref="D24:E24" si="4">D8*0.0036</f>
+        <v>392.54883965396471</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="4"/>
+        <v>454.6970151947001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <f>C9*0.0036</f>
+        <v>212.24268814826934</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ref="D25:E25" si="5">D9*0.0036</f>
+        <v>210.39356034603534</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="5"/>
+        <v>243.70298480529993</v>
+      </c>
+    </row>
     <row r="27" spans="2:12" ht="16.5" customHeight="1"/>
     <row r="34" spans="12:29">
       <c r="L34" t="s">
@@ -7440,8 +7517,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C23:I23"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <hyperlinks>
@@ -7456,18 +7534,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:G17"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18">
+    <row r="2" spans="2:7" ht="17.399999999999999">
       <c r="B2" s="16" t="s">
         <v>66</v>
       </c>
@@ -7506,7 +7584,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="31.9" customHeight="1">
+    <row r="6" spans="2:7" ht="31.95" customHeight="1">
       <c r="B6" s="20" t="s">
         <v>73</v>
       </c>
@@ -7605,26 +7683,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="853a583b-5a39-49db-b57b-0c8a2ee0f312" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45d80b71-d53a-4925-9636-d69011c62a0b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100478D9ACB663A0B44ABC718894EB3A5FF" ma:contentTypeVersion="12" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="9b81457e3208e76a02f6602a4efc0f0c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45d80b71-d53a-4925-9636-d69011c62a0b" xmlns:ns3="853a583b-5a39-49db-b57b-0c8a2ee0f312" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6516941b06c58921cbe989d74b07aab8" ns2:_="" ns3:_="">
     <xsd:import namespace="45d80b71-d53a-4925-9636-d69011c62a0b"/>
@@ -7825,26 +7883,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="853a583b-5a39-49db-b57b-0c8a2ee0f312"/>
-    <ds:schemaRef ds:uri="45d80b71-d53a-4925-9636-d69011c62a0b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="853a583b-5a39-49db-b57b-0c8a2ee0f312" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45d80b71-d53a-4925-9636-d69011c62a0b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522C4796-8A91-41DD-90B2-C654F53C909D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7861,4 +7920,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="853a583b-5a39-49db-b57b-0c8a2ee0f312"/>
+    <ds:schemaRef ds:uri="45d80b71-d53a-4925-9636-d69011c62a0b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>